--- a/data/trans_orig/IP22D4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Provincia-trans_orig.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>52863</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>94100</t>
+          <t>94306</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D4_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,64 +1632,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7589</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5909</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7986</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4869</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8505</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,27 +2163,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2314,82 +2314,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,64 +2544,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,27 +3461,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3496,27 +3496,27 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>22854</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,102 +4373,102 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>41616</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>37864</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>51507</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>47283</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>52863</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>88504</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>84107</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>90584</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>96,69%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>98249</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>94306</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>100353</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -4594,82 +4594,82 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
